--- a/Артефакт 3. Фин модель и юнит-экономика — Попутчик.xlsx
+++ b/Артефакт 3. Фин модель и юнит-экономика — Попутчик.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Допущения" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Юнит-экономика" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фин модель (12 мес)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет 500к" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стресс-тест" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Допущения" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Юнит-экономика" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фин модель (12 мес)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет 500к" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="#,##0.00;(#,##0.00);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,15 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +138,11 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -143,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -322,6 +335,11 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -685,7 +703,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="78" t="inlineStr">
         <is>
-          <t>Попутчик: результаты выбранного сценария</t>
+          <t>Система Попутчик: результаты выбранного сценария</t>
         </is>
       </c>
     </row>
@@ -921,6 +939,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="108" t="inlineStr">
+        <is>
+          <t>Попутчик: стресс-тест базового сценария</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Меняем по одному допущению, остальное как в базе. Посчитано той же логикой, что лист «Фин модель (12 мес)»; при подстановке параметров в «Допущения» цифры воспроизводятся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="109" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B4" s="109" t="inlineStr">
+        <is>
+          <t>Маржа с заказа, ₽</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
+        <is>
+          <t>LTV, ₽</t>
+        </is>
+      </c>
+      <c r="D4" s="109" t="inlineStr">
+        <is>
+          <t>LTV / CAC</t>
+        </is>
+      </c>
+      <c r="E4" s="109" t="inlineStr">
+        <is>
+          <t>Активных к М6</t>
+        </is>
+      </c>
+      <c r="F4" s="109" t="inlineStr">
+        <is>
+          <t>Первый месяц в плюс</t>
+        </is>
+      </c>
+      <c r="G4" s="109" t="inlineStr">
+        <is>
+          <t>500 тыс. вернулись</t>
+        </is>
+      </c>
+      <c r="H4" s="109" t="inlineStr">
+        <is>
+          <t>Минимум денег за 12 мес, тыс. ₽</t>
+        </is>
+      </c>
+      <c r="I4" s="109" t="inlineStr">
+        <is>
+          <t>Деньги к М12, тыс. ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>База</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C5" t="n">
+        <v>829</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>749</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>М4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>М7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAC ×2 (400 ₽)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C6" t="n">
+        <v>829</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>375</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>М6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>М12</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>252</v>
+      </c>
+      <c r="I6" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Удержание 65% вместо 75%</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>69</v>
+      </c>
+      <c r="C7" t="n">
+        <v>592</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>650</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>М4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>М7</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>299</v>
+      </c>
+      <c r="I7" t="n">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Курьер 120 ₽ (2,5 заказа в рейсе)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>49</v>
+      </c>
+      <c r="C8" t="n">
+        <v>589</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>749</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>М5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>М8</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>284</v>
+      </c>
+      <c r="I8" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Средний чек 900 ₽ вместо 1 200</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>559</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>749</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>М5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>М9</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>279</v>
+      </c>
+      <c r="I9" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAC ×2 и курьер 120 ₽ вместе</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n">
+        <v>589</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>375</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>М7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>нет за 12 мес</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>206</v>
+      </c>
+      <c r="I10" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Пилот не прошёл → стоп-правило (маркетинг выкл.)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>49</v>
+      </c>
+      <c r="C11" t="n">
+        <v>589</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="110" t="inlineStr">
+        <is>
+          <t>Вывод: ни в одном сценарии деньги не уходят ниже ~200 тыс. ₽. При CAC ×2 проект всё равно окупается за 12 месяцев; при одновременном ухудшении двух допущений — включается стоп-правило и сохраняется бюджет.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -935,7 +1291,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>Попутчик: допущения</t>
+          <t>Система Попутчик: допущения</t>
         </is>
       </c>
       <c r="B1" s="23" t="n"/>
@@ -1449,7 +1805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1465,7 +1821,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>Попутчик: экономика заказа и клиента</t>
+          <t>Система Попутчик: экономика заказа и клиента</t>
         </is>
       </c>
       <c r="B1" s="23" t="n"/>
@@ -1590,7 +1946,7 @@
           <t>LTV (по марже), ₽</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="77">
         <f>B11*B12</f>
         <v/>
       </c>
@@ -1628,7 +1984,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
         <is>
@@ -1636,27 +1991,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -1676,7 +2010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1704,7 +2038,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>Попутчик: 12 месяцев с начала разработки</t>
+          <t>Система Попутчик: 12 месяцев с начала разработки</t>
         </is>
       </c>
       <c r="B1" s="23" t="n"/>
@@ -3345,7 +3679,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -3365,7 +3698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3382,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>Попутчик: бюджет на первые шесть месяцев</t>
+          <t>Система Попутчик: бюджет на первые шесть месяцев</t>
         </is>
       </c>
       <c r="B1" s="23" t="n"/>
@@ -3497,37 +3830,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
